--- a/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251216/For Winter Ending (Actual)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Tickets</t>
   </si>
   <si>
+    <t xml:space="preserve">                         </t>
+  </si>
+  <si>
     <t xml:space="preserve">D1500                    </t>
   </si>
   <si>
@@ -40,13 +43,13 @@
     <t xml:space="preserve">T104                     </t>
   </si>
   <si>
+    <t xml:space="preserve">T103                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t xml:space="preserve">T257                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T103                     </t>
   </si>
   <si>
     <t>Ski School</t>
@@ -489,9 +492,11 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2">
         <v>-4592.4200</v>
@@ -502,10 +507,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D3" s="2">
         <v>130.9000</v>
@@ -516,10 +521,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2">
         <v>-17.9500</v>
@@ -530,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>1807394.8500</v>
+        <v>156018.9100</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -544,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2">
-        <v>228.0400</v>
+        <v>1807394.8500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -558,22 +563,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2">
-        <v>156018.9100</v>
+        <v>228.0400</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
         <v>205184.6000</v>
@@ -581,11 +586,11 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2">
         <v>551196.1700</v>
@@ -593,11 +598,11 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2">
         <v>288384.9700</v>
@@ -605,11 +610,11 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2">
         <v>197.4600</v>
@@ -617,11 +622,11 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2">
         <v>303513.3000</v>
@@ -629,11 +634,11 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2">
         <v>371913.9500</v>
@@ -641,11 +646,11 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2">
         <v>37557.7200</v>
@@ -653,11 +658,11 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
         <v>13983.7500</v>
@@ -665,11 +670,11 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2">
         <v>0.0500</v>
